--- a/worklog/v2.2.3/s10/pjm/v2/metrics/项目指标列表.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v2/metrics/项目指标列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10695"/>
+    <workbookView windowWidth="23040" windowHeight="9225"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -252,11 +252,11 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -264,14 +264,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -279,7 +272,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -287,14 +280,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -302,7 +295,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -310,7 +303,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -318,7 +311,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -326,7 +319,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -334,14 +327,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -349,7 +342,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -357,7 +350,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -365,14 +358,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -380,52 +373,58 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -792,133 +791,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -929,72 +928,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1470,15 +1469,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="8.96666666666667" defaultRowHeight="17.6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.96296296296296" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.96666666666667" style="1"/>
-    <col min="2" max="2" width="22.6333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.96666666666667" style="1"/>
+    <col min="1" max="1" width="8.96296296296296" style="1"/>
+    <col min="2" max="2" width="22.6296296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68.3407407407407" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.96296296296296" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.65" spans="1:3">
+    <row r="1" ht="31" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +1488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="35.25" spans="1:3">
+    <row r="2" ht="54" customHeight="1" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1554,7 +1553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="52.9" spans="1:3">
+    <row r="9" ht="35.25" spans="1:3">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -1655,7 +1654,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="70.5" spans="1:3">
+    <row r="20" ht="52.9" spans="1:3">
       <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
@@ -1666,7 +1665,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" ht="70.5" spans="1:3">
+    <row r="21" ht="52.9" spans="1:3">
       <c r="A21" s="5"/>
       <c r="B21" s="4" t="s">
         <v>42</v>
@@ -1675,7 +1674,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" ht="70.5" spans="1:3">
+    <row r="22" ht="52.9" spans="1:3">
       <c r="A22" s="5"/>
       <c r="B22" s="4" t="s">
         <v>44</v>
@@ -1684,7 +1683,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" ht="70.5" spans="1:3">
+    <row r="23" ht="52.9" spans="1:3">
       <c r="A23" s="5"/>
       <c r="B23" s="4" t="s">
         <v>46</v>
@@ -1693,7 +1692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="70.5" spans="1:3">
+    <row r="24" ht="52.9" spans="1:3">
       <c r="A24" s="6"/>
       <c r="B24" s="4" t="s">
         <v>48</v>
@@ -1702,7 +1701,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" ht="52.9" spans="1:3">
+    <row r="25" ht="35.25" spans="1:3">
       <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
@@ -1722,7 +1721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" ht="52.9" spans="1:3">
+    <row r="27" ht="35.25" spans="1:3">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
         <v>55</v>
@@ -1785,7 +1784,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" ht="52.9" spans="1:3">
+    <row r="34" ht="35.25" spans="1:3">
       <c r="A34" s="5"/>
       <c r="B34" s="4" t="s">
         <v>51</v>
@@ -1794,7 +1793,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" ht="70.5" spans="1:3">
+    <row r="35" ht="52.9" spans="1:3">
       <c r="A35" s="6"/>
       <c r="B35" s="4" t="s">
         <v>53</v>
